--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135445043</v>
+        <v>136916429</v>
       </c>
       <c r="B11" t="n">
-        <v>92027</v>
+        <v>101536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1739,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613775</v>
+        <v>613803</v>
       </c>
       <c r="R11" t="n">
-        <v>7100634</v>
+        <v>7100627</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,39 +1795,35 @@
           <t>Åsele</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>AC-Åse-0045</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1833,21 +1833,21 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445043</t>
+          <t>https://artportalen.se/Sighting/136916429</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135445045</v>
+        <v>136916431</v>
       </c>
       <c r="B12" t="n">
-        <v>92027</v>
+        <v>101536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,37 +1855,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613799</v>
+        <v>613699</v>
       </c>
       <c r="R12" t="n">
-        <v>7100628</v>
+        <v>7100529</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1910,24 +1911,19 @@
           <t>Åsele</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>AC-Åse-0044</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,7 +1939,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1953,43 +1949,43 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445045</t>
+          <t>https://artportalen.se/Sighting/136916431</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445042</v>
+        <v>135445043</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>92027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613767</v>
+        <v>613775</v>
       </c>
       <c r="R13" t="n">
-        <v>7100672</v>
+        <v>7100634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2034,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,41 +2070,44 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445042</t>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445044</v>
+        <v>135445045</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
@@ -2118,7 +2117,7 @@
         <v>613799</v>
       </c>
       <c r="R14" t="n">
-        <v>7100626</v>
+        <v>7100628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2169,6 +2168,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445044</t>
+          <t>https://artportalen.se/Sighting/135445045</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445055</v>
+        <v>135445042</v>
       </c>
       <c r="B15" t="n">
         <v>79443</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613807</v>
+        <v>613767</v>
       </c>
       <c r="R15" t="n">
-        <v>7100543</v>
+        <v>7100672</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,13 +2306,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445055</t>
+          <t>https://artportalen.se/Sighting/135445042</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445060</v>
+        <v>135445044</v>
       </c>
       <c r="B16" t="n">
         <v>79443</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613717</v>
+        <v>613799</v>
       </c>
       <c r="R16" t="n">
-        <v>7100503</v>
+        <v>7100626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,13 +2422,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445060</t>
+          <t>https://artportalen.se/Sighting/135445044</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445065</v>
+        <v>135445055</v>
       </c>
       <c r="B17" t="n">
         <v>79443</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613671</v>
+        <v>613807</v>
       </c>
       <c r="R17" t="n">
-        <v>7100521</v>
+        <v>7100543</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,13 +2538,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445065</t>
+          <t>https://artportalen.se/Sighting/135445055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135445068</v>
+        <v>135445060</v>
       </c>
       <c r="B18" t="n">
         <v>79443</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613584</v>
+        <v>613717</v>
       </c>
       <c r="R18" t="n">
-        <v>7100548</v>
+        <v>7100503</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,56 +2654,51 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445068</t>
+          <t>https://artportalen.se/Sighting/135445060</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135445049</v>
+        <v>135445065</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613792</v>
+        <v>613671</v>
       </c>
       <c r="R19" t="n">
-        <v>7100584</v>
+        <v>7100521</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,19 +2740,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2780,56 +2770,51 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445049</t>
+          <t>https://artportalen.se/Sighting/135445065</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135445057</v>
+        <v>135445068</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613781</v>
+        <v>613584</v>
       </c>
       <c r="R20" t="n">
-        <v>7100499</v>
+        <v>7100548</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2861,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,13 +2886,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445057</t>
+          <t>https://artportalen.se/Sighting/135445068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445059</v>
+        <v>135445049</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -2936,16 +2921,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613721</v>
+        <v>613792</v>
       </c>
       <c r="R21" t="n">
-        <v>7100491</v>
+        <v>7100584</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2977,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3022,13 +3012,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445059</t>
+          <t>https://artportalen.se/Sighting/135445049</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135445069</v>
+        <v>135445057</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3057,16 +3047,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613582</v>
+        <v>613781</v>
       </c>
       <c r="R22" t="n">
-        <v>7100539</v>
+        <v>7100499</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3098,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,19 +3103,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3143,13 +3133,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445069</t>
+          <t>https://artportalen.se/Sighting/135445057</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135445072</v>
+        <v>135445059</v>
       </c>
       <c r="B23" t="n">
         <v>57982</v>
@@ -3178,21 +3168,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613316</v>
+        <v>613721</v>
       </c>
       <c r="R23" t="n">
-        <v>7100665</v>
+        <v>7100491</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3224,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,14 +3219,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3264,13 +3254,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445072</t>
+          <t>https://artportalen.se/Sighting/135445059</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135445073</v>
+        <v>135445069</v>
       </c>
       <c r="B24" t="n">
         <v>57982</v>
@@ -3299,21 +3289,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613305</v>
+        <v>613582</v>
       </c>
       <c r="R24" t="n">
-        <v>7100667</v>
+        <v>7100539</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3345,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3355,14 +3340,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3385,13 +3375,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445073</t>
+          <t>https://artportalen.se/Sighting/135445069</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135445074</v>
+        <v>135445072</v>
       </c>
       <c r="B25" t="n">
         <v>57982</v>
@@ -3422,7 +3412,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3431,13 +3421,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613337</v>
+        <v>613316</v>
       </c>
       <c r="R25" t="n">
-        <v>7100678</v>
+        <v>7100665</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,7 +3456,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3476,7 +3466,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,13 +3496,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445074</t>
+          <t>https://artportalen.se/Sighting/135445072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445076</v>
+        <v>135445073</v>
       </c>
       <c r="B26" t="n">
         <v>57982</v>
@@ -3541,16 +3531,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613591</v>
+        <v>613305</v>
       </c>
       <c r="R26" t="n">
-        <v>7100642</v>
+        <v>7100667</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3582,7 +3577,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3592,19 +3587,14 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3627,13 +3617,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445076</t>
+          <t>https://artportalen.se/Sighting/135445073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135445079</v>
+        <v>135445074</v>
       </c>
       <c r="B27" t="n">
         <v>57982</v>
@@ -3673,13 +3663,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613654</v>
+        <v>613337</v>
       </c>
       <c r="R27" t="n">
-        <v>7100656</v>
+        <v>7100678</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3708,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3718,7 +3708,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,16 +3738,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445079</t>
+          <t>https://artportalen.se/Sighting/135445074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135445070</v>
+        <v>135445076</v>
       </c>
       <c r="B28" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,42 +3755,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613505</v>
+        <v>613591</v>
       </c>
       <c r="R28" t="n">
-        <v>7100621</v>
+        <v>7100642</v>
       </c>
       <c r="S28" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3829,7 +3814,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3839,14 +3824,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3869,54 +3859,59 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445070</t>
+          <t>https://artportalen.se/Sighting/135445076</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135445052</v>
+        <v>135445079</v>
       </c>
       <c r="B29" t="n">
-        <v>99315</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613795</v>
+        <v>613654</v>
       </c>
       <c r="R29" t="n">
-        <v>7100557</v>
+        <v>7100656</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,54 +3980,59 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445052</t>
+          <t>https://artportalen.se/Sighting/135445079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135445058</v>
+        <v>135445070</v>
       </c>
       <c r="B30" t="n">
-        <v>99315</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613724</v>
+        <v>613505</v>
       </c>
       <c r="R30" t="n">
-        <v>7100494</v>
+        <v>7100621</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445058</t>
+          <t>https://artportalen.se/Sighting/135445070</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135445067</v>
+        <v>135445052</v>
       </c>
       <c r="B31" t="n">
         <v>99315</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613619</v>
+        <v>613795</v>
       </c>
       <c r="R31" t="n">
-        <v>7100553</v>
+        <v>7100557</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4216,6 +4216,238 @@
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445052</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135445058</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ystaåmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>613724</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7100494</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445058</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135445067</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ystaåmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>613619</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7100553</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445067</t>
         </is>
@@ -4253,6 +4485,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136916429</v>
+        <v>136916431</v>
       </c>
       <c r="B11" t="n">
         <v>101536</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613803</v>
+        <v>613699</v>
       </c>
       <c r="R11" t="n">
-        <v>7100627</v>
+        <v>7100529</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AC-Åse-0045</t>
+          <t>AC-Åse-0044</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1838,16 +1838,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916429</t>
+          <t>https://artportalen.se/Sighting/136916431</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136916431</v>
+        <v>135445043</v>
       </c>
       <c r="B12" t="n">
-        <v>101536</v>
+        <v>92027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,38 +1855,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613699</v>
+        <v>613775</v>
       </c>
       <c r="R12" t="n">
-        <v>7100529</v>
+        <v>7100634</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1911,35 +1907,39 @@
           <t>Åsele</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>AC-Åse-0044</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1949,18 +1949,18 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916431</t>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445043</v>
+        <v>135445045</v>
       </c>
       <c r="B13" t="n">
         <v>92027</v>
@@ -1989,16 +1989,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613775</v>
+        <v>613799</v>
       </c>
       <c r="R13" t="n">
-        <v>7100634</v>
+        <v>7100628</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,6 +2052,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2070,54 +2074,51 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445043</t>
+          <t>https://artportalen.se/Sighting/135445045</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445045</v>
+        <v>135445042</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613799</v>
+        <v>613767</v>
       </c>
       <c r="R14" t="n">
-        <v>7100628</v>
+        <v>7100672</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2149,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,7 +2169,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445045</t>
+          <t>https://artportalen.se/Sighting/135445042</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445042</v>
+        <v>135445044</v>
       </c>
       <c r="B15" t="n">
         <v>79443</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613767</v>
+        <v>613799</v>
       </c>
       <c r="R15" t="n">
-        <v>7100672</v>
+        <v>7100626</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,13 +2306,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445042</t>
+          <t>https://artportalen.se/Sighting/135445044</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445044</v>
+        <v>135445055</v>
       </c>
       <c r="B16" t="n">
         <v>79443</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613799</v>
+        <v>613807</v>
       </c>
       <c r="R16" t="n">
-        <v>7100626</v>
+        <v>7100543</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,13 +2422,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445044</t>
+          <t>https://artportalen.se/Sighting/135445055</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445055</v>
+        <v>135445060</v>
       </c>
       <c r="B17" t="n">
         <v>79443</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613807</v>
+        <v>613717</v>
       </c>
       <c r="R17" t="n">
-        <v>7100543</v>
+        <v>7100503</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,13 +2538,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445055</t>
+          <t>https://artportalen.se/Sighting/135445060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135445060</v>
+        <v>135445065</v>
       </c>
       <c r="B18" t="n">
         <v>79443</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613717</v>
+        <v>613671</v>
       </c>
       <c r="R18" t="n">
-        <v>7100503</v>
+        <v>7100521</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445060</t>
+          <t>https://artportalen.se/Sighting/135445065</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135445065</v>
+        <v>135445068</v>
       </c>
       <c r="B19" t="n">
         <v>79443</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613671</v>
+        <v>613584</v>
       </c>
       <c r="R19" t="n">
-        <v>7100521</v>
+        <v>7100548</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,51 +2770,56 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445065</t>
+          <t>https://artportalen.se/Sighting/135445068</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135445068</v>
+        <v>135445049</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613584</v>
+        <v>613792</v>
       </c>
       <c r="R20" t="n">
-        <v>7100548</v>
+        <v>7100584</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2846,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,14 +2861,19 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2886,13 +2896,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445068</t>
+          <t>https://artportalen.se/Sighting/135445049</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445049</v>
+        <v>135445057</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -2923,7 +2933,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2932,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613792</v>
+        <v>613781</v>
       </c>
       <c r="R21" t="n">
-        <v>7100584</v>
+        <v>7100499</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2967,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,19 +2987,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3012,13 +3017,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445049</t>
+          <t>https://artportalen.se/Sighting/135445057</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135445057</v>
+        <v>135445059</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3047,21 +3052,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613781</v>
+        <v>613721</v>
       </c>
       <c r="R22" t="n">
-        <v>7100499</v>
+        <v>7100491</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,14 +3103,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3133,13 +3138,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445057</t>
+          <t>https://artportalen.se/Sighting/135445059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135445059</v>
+        <v>135445069</v>
       </c>
       <c r="B23" t="n">
         <v>57982</v>
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613721</v>
+        <v>613582</v>
       </c>
       <c r="R23" t="n">
-        <v>7100491</v>
+        <v>7100539</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3209,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3219,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3254,13 +3259,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445059</t>
+          <t>https://artportalen.se/Sighting/135445069</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135445069</v>
+        <v>135445072</v>
       </c>
       <c r="B24" t="n">
         <v>57982</v>
@@ -3289,16 +3294,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613582</v>
+        <v>613316</v>
       </c>
       <c r="R24" t="n">
-        <v>7100539</v>
+        <v>7100665</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3330,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,19 +3350,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3375,13 +3380,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445069</t>
+          <t>https://artportalen.se/Sighting/135445072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135445072</v>
+        <v>135445073</v>
       </c>
       <c r="B25" t="n">
         <v>57982</v>
@@ -3421,10 +3426,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613316</v>
+        <v>613305</v>
       </c>
       <c r="R25" t="n">
-        <v>7100665</v>
+        <v>7100667</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,7 +3461,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3466,7 +3471,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3496,13 +3501,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445072</t>
+          <t>https://artportalen.se/Sighting/135445073</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445073</v>
+        <v>135445074</v>
       </c>
       <c r="B26" t="n">
         <v>57982</v>
@@ -3533,7 +3538,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3542,13 +3547,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613305</v>
+        <v>613337</v>
       </c>
       <c r="R26" t="n">
-        <v>7100667</v>
+        <v>7100678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3577,7 +3582,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3587,7 +3592,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3617,13 +3622,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445073</t>
+          <t>https://artportalen.se/Sighting/135445074</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135445074</v>
+        <v>135445076</v>
       </c>
       <c r="B27" t="n">
         <v>57982</v>
@@ -3652,24 +3657,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613337</v>
+        <v>613591</v>
       </c>
       <c r="R27" t="n">
-        <v>7100678</v>
+        <v>7100642</v>
       </c>
       <c r="S27" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3708,14 +3708,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3738,13 +3743,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445074</t>
+          <t>https://artportalen.se/Sighting/135445076</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135445076</v>
+        <v>135445079</v>
       </c>
       <c r="B28" t="n">
         <v>57982</v>
@@ -3773,19 +3778,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613591</v>
+        <v>613654</v>
       </c>
       <c r="R28" t="n">
-        <v>7100642</v>
+        <v>7100656</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3814,7 +3824,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3824,19 +3834,14 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3859,16 +3864,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445076</t>
+          <t>https://artportalen.se/Sighting/135445079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135445079</v>
+        <v>135445070</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,27 +3881,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3905,13 +3910,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613654</v>
+        <v>613505</v>
       </c>
       <c r="R29" t="n">
-        <v>7100656</v>
+        <v>7100621</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3940,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,7 +3955,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,59 +3985,54 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445079</t>
+          <t>https://artportalen.se/Sighting/135445070</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135445070</v>
+        <v>135445052</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>99315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613505</v>
+        <v>613795</v>
       </c>
       <c r="R30" t="n">
-        <v>7100621</v>
+        <v>7100557</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445070</t>
+          <t>https://artportalen.se/Sighting/135445052</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135445052</v>
+        <v>135445058</v>
       </c>
       <c r="B31" t="n">
         <v>99315</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613795</v>
+        <v>613724</v>
       </c>
       <c r="R31" t="n">
-        <v>7100557</v>
+        <v>7100494</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,13 +4217,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445052</t>
+          <t>https://artportalen.se/Sighting/135445058</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135445058</v>
+        <v>135445067</v>
       </c>
       <c r="B32" t="n">
         <v>99315</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613724</v>
+        <v>613619</v>
       </c>
       <c r="R32" t="n">
-        <v>7100494</v>
+        <v>7100553</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,122 +4332,6 @@
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135445058</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>135445067</v>
-      </c>
-      <c r="B33" t="n">
-        <v>99315</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Ystaåmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>613619</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7100553</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445067</t>
         </is>
@@ -4486,7 +4370,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136916431</v>
+        <v>136916429</v>
       </c>
       <c r="B11" t="n">
         <v>101536</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613699</v>
+        <v>613803</v>
       </c>
       <c r="R11" t="n">
-        <v>7100529</v>
+        <v>7100627</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AC-Åse-0044</t>
+          <t>AC-Åse-0045</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1838,16 +1838,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916431</t>
+          <t>https://artportalen.se/Sighting/136916429</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135445043</v>
+        <v>136916431</v>
       </c>
       <c r="B12" t="n">
-        <v>92027</v>
+        <v>101536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,34 +1855,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613775</v>
+        <v>613699</v>
       </c>
       <c r="R12" t="n">
-        <v>7100634</v>
+        <v>7100529</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,39 +1911,35 @@
           <t>Åsele</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>AC-Åse-0044</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1949,18 +1949,18 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445043</t>
+          <t>https://artportalen.se/Sighting/136916431</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445045</v>
+        <v>135445043</v>
       </c>
       <c r="B13" t="n">
         <v>92027</v>
@@ -1989,19 +1989,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613799</v>
+        <v>613775</v>
       </c>
       <c r="R13" t="n">
-        <v>7100628</v>
+        <v>7100634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,7 +2049,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2074,51 +2070,54 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445045</t>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445042</v>
+        <v>135445045</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613767</v>
+        <v>613799</v>
       </c>
       <c r="R14" t="n">
-        <v>7100672</v>
+        <v>7100628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2150,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,6 +2168,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445042</t>
+          <t>https://artportalen.se/Sighting/135445045</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445044</v>
+        <v>135445042</v>
       </c>
       <c r="B15" t="n">
         <v>79443</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613799</v>
+        <v>613767</v>
       </c>
       <c r="R15" t="n">
-        <v>7100626</v>
+        <v>7100672</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,13 +2306,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445044</t>
+          <t>https://artportalen.se/Sighting/135445042</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445055</v>
+        <v>135445044</v>
       </c>
       <c r="B16" t="n">
         <v>79443</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613807</v>
+        <v>613799</v>
       </c>
       <c r="R16" t="n">
-        <v>7100543</v>
+        <v>7100626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,13 +2422,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445055</t>
+          <t>https://artportalen.se/Sighting/135445044</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445060</v>
+        <v>135445055</v>
       </c>
       <c r="B17" t="n">
         <v>79443</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613717</v>
+        <v>613807</v>
       </c>
       <c r="R17" t="n">
-        <v>7100503</v>
+        <v>7100543</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,13 +2538,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445060</t>
+          <t>https://artportalen.se/Sighting/135445055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135445065</v>
+        <v>135445060</v>
       </c>
       <c r="B18" t="n">
         <v>79443</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613671</v>
+        <v>613717</v>
       </c>
       <c r="R18" t="n">
-        <v>7100521</v>
+        <v>7100503</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445065</t>
+          <t>https://artportalen.se/Sighting/135445060</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135445068</v>
+        <v>135445065</v>
       </c>
       <c r="B19" t="n">
         <v>79443</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613584</v>
+        <v>613671</v>
       </c>
       <c r="R19" t="n">
-        <v>7100548</v>
+        <v>7100521</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,56 +2770,51 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445068</t>
+          <t>https://artportalen.se/Sighting/135445065</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135445049</v>
+        <v>135445068</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613792</v>
+        <v>613584</v>
       </c>
       <c r="R20" t="n">
-        <v>7100584</v>
+        <v>7100548</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,19 +2856,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2896,13 +2886,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445049</t>
+          <t>https://artportalen.se/Sighting/135445068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445057</v>
+        <v>135445049</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -2933,7 +2923,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613781</v>
+        <v>613792</v>
       </c>
       <c r="R21" t="n">
-        <v>7100499</v>
+        <v>7100584</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2977,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,14 +2977,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3017,13 +3012,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445057</t>
+          <t>https://artportalen.se/Sighting/135445049</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135445059</v>
+        <v>135445057</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3052,16 +3047,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613721</v>
+        <v>613781</v>
       </c>
       <c r="R22" t="n">
-        <v>7100491</v>
+        <v>7100499</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,19 +3103,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3138,13 +3133,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445059</t>
+          <t>https://artportalen.se/Sighting/135445057</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135445069</v>
+        <v>135445059</v>
       </c>
       <c r="B23" t="n">
         <v>57982</v>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613582</v>
+        <v>613721</v>
       </c>
       <c r="R23" t="n">
-        <v>7100539</v>
+        <v>7100491</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3214,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3219,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3259,13 +3254,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445069</t>
+          <t>https://artportalen.se/Sighting/135445059</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135445072</v>
+        <v>135445069</v>
       </c>
       <c r="B24" t="n">
         <v>57982</v>
@@ -3294,21 +3289,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613316</v>
+        <v>613582</v>
       </c>
       <c r="R24" t="n">
-        <v>7100665</v>
+        <v>7100539</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3340,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,14 +3340,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3380,13 +3375,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445072</t>
+          <t>https://artportalen.se/Sighting/135445069</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135445073</v>
+        <v>135445072</v>
       </c>
       <c r="B25" t="n">
         <v>57982</v>
@@ -3426,10 +3421,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613305</v>
+        <v>613316</v>
       </c>
       <c r="R25" t="n">
-        <v>7100667</v>
+        <v>7100665</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3461,7 +3456,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3471,7 +3466,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3501,13 +3496,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445073</t>
+          <t>https://artportalen.se/Sighting/135445072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445074</v>
+        <v>135445073</v>
       </c>
       <c r="B26" t="n">
         <v>57982</v>
@@ -3538,7 +3533,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3547,13 +3542,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613337</v>
+        <v>613305</v>
       </c>
       <c r="R26" t="n">
-        <v>7100678</v>
+        <v>7100667</v>
       </c>
       <c r="S26" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3582,7 +3577,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3592,7 +3587,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,13 +3617,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445074</t>
+          <t>https://artportalen.se/Sighting/135445073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135445076</v>
+        <v>135445074</v>
       </c>
       <c r="B27" t="n">
         <v>57982</v>
@@ -3657,19 +3652,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613591</v>
+        <v>613337</v>
       </c>
       <c r="R27" t="n">
-        <v>7100642</v>
+        <v>7100678</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3708,19 +3708,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3743,13 +3738,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445076</t>
+          <t>https://artportalen.se/Sighting/135445074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135445079</v>
+        <v>135445076</v>
       </c>
       <c r="B28" t="n">
         <v>57982</v>
@@ -3778,24 +3773,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613654</v>
+        <v>613591</v>
       </c>
       <c r="R28" t="n">
-        <v>7100656</v>
+        <v>7100642</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,7 +3814,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3834,14 +3824,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3864,16 +3859,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445079</t>
+          <t>https://artportalen.se/Sighting/135445076</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135445070</v>
+        <v>135445079</v>
       </c>
       <c r="B29" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,27 +3876,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3910,13 +3905,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613505</v>
+        <v>613654</v>
       </c>
       <c r="R29" t="n">
-        <v>7100621</v>
+        <v>7100656</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,54 +3980,59 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445070</t>
+          <t>https://artportalen.se/Sighting/135445079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135445052</v>
+        <v>135445070</v>
       </c>
       <c r="B30" t="n">
-        <v>99315</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613795</v>
+        <v>613505</v>
       </c>
       <c r="R30" t="n">
-        <v>7100557</v>
+        <v>7100621</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445052</t>
+          <t>https://artportalen.se/Sighting/135445070</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135445058</v>
+        <v>135445052</v>
       </c>
       <c r="B31" t="n">
         <v>99315</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613724</v>
+        <v>613795</v>
       </c>
       <c r="R31" t="n">
-        <v>7100494</v>
+        <v>7100557</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,13 +4217,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445058</t>
+          <t>https://artportalen.se/Sighting/135445052</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135445067</v>
+        <v>135445058</v>
       </c>
       <c r="B32" t="n">
         <v>99315</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613619</v>
+        <v>613724</v>
       </c>
       <c r="R32" t="n">
-        <v>7100553</v>
+        <v>7100494</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,6 +4332,122 @@
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445058</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135445067</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ystaåmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>613619</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7100553</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445067</t>
         </is>
@@ -4370,6 +4486,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136916431</v>
       </c>
       <c r="B11" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136916431</v>
       </c>
       <c r="B11" t="n">
-        <v>101542</v>
+        <v>101544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136916431</v>
+        <v>136916429</v>
       </c>
       <c r="B11" t="n">
-        <v>101544</v>
+        <v>101545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613699</v>
+        <v>613803</v>
       </c>
       <c r="R11" t="n">
-        <v>7100529</v>
+        <v>7100627</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AC-Åse-0044</t>
+          <t>AC-Åse-0045</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1838,16 +1838,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916431</t>
+          <t>https://artportalen.se/Sighting/136916429</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135445043</v>
+        <v>136916431</v>
       </c>
       <c r="B12" t="n">
-        <v>92027</v>
+        <v>101545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,34 +1855,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613775</v>
+        <v>613699</v>
       </c>
       <c r="R12" t="n">
-        <v>7100634</v>
+        <v>7100529</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,39 +1911,35 @@
           <t>Åsele</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>AC-Åse-0044</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:14</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1949,18 +1949,18 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445043</t>
+          <t>https://artportalen.se/Sighting/136916431</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445045</v>
+        <v>135445043</v>
       </c>
       <c r="B13" t="n">
         <v>92027</v>
@@ -1989,19 +1989,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613799</v>
+        <v>613775</v>
       </c>
       <c r="R13" t="n">
-        <v>7100628</v>
+        <v>7100634</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,7 +2049,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2074,51 +2070,54 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445045</t>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445042</v>
+        <v>135445045</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613767</v>
+        <v>613799</v>
       </c>
       <c r="R14" t="n">
-        <v>7100672</v>
+        <v>7100628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2150,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2159,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,6 +2168,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445042</t>
+          <t>https://artportalen.se/Sighting/135445045</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445044</v>
+        <v>135445042</v>
       </c>
       <c r="B15" t="n">
         <v>79443</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613799</v>
+        <v>613767</v>
       </c>
       <c r="R15" t="n">
-        <v>7100626</v>
+        <v>7100672</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,13 +2306,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445044</t>
+          <t>https://artportalen.se/Sighting/135445042</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445055</v>
+        <v>135445044</v>
       </c>
       <c r="B16" t="n">
         <v>79443</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613807</v>
+        <v>613799</v>
       </c>
       <c r="R16" t="n">
-        <v>7100543</v>
+        <v>7100626</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,13 +2422,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445055</t>
+          <t>https://artportalen.se/Sighting/135445044</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445060</v>
+        <v>135445055</v>
       </c>
       <c r="B17" t="n">
         <v>79443</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613717</v>
+        <v>613807</v>
       </c>
       <c r="R17" t="n">
-        <v>7100503</v>
+        <v>7100543</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,13 +2538,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445060</t>
+          <t>https://artportalen.se/Sighting/135445055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135445065</v>
+        <v>135445060</v>
       </c>
       <c r="B18" t="n">
         <v>79443</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613671</v>
+        <v>613717</v>
       </c>
       <c r="R18" t="n">
-        <v>7100521</v>
+        <v>7100503</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445065</t>
+          <t>https://artportalen.se/Sighting/135445060</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135445068</v>
+        <v>135445065</v>
       </c>
       <c r="B19" t="n">
         <v>79443</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613584</v>
+        <v>613671</v>
       </c>
       <c r="R19" t="n">
-        <v>7100548</v>
+        <v>7100521</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,56 +2770,51 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445068</t>
+          <t>https://artportalen.se/Sighting/135445065</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135445049</v>
+        <v>135445068</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613792</v>
+        <v>613584</v>
       </c>
       <c r="R20" t="n">
-        <v>7100584</v>
+        <v>7100548</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,19 +2856,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2896,13 +2886,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445049</t>
+          <t>https://artportalen.se/Sighting/135445068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445057</v>
+        <v>135445049</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -2933,7 +2923,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613781</v>
+        <v>613792</v>
       </c>
       <c r="R21" t="n">
-        <v>7100499</v>
+        <v>7100584</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2977,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,14 +2977,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3017,13 +3012,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445057</t>
+          <t>https://artportalen.se/Sighting/135445049</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135445059</v>
+        <v>135445057</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3052,16 +3047,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613721</v>
+        <v>613781</v>
       </c>
       <c r="R22" t="n">
-        <v>7100491</v>
+        <v>7100499</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,19 +3103,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3138,13 +3133,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445059</t>
+          <t>https://artportalen.se/Sighting/135445057</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135445069</v>
+        <v>135445059</v>
       </c>
       <c r="B23" t="n">
         <v>57982</v>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613582</v>
+        <v>613721</v>
       </c>
       <c r="R23" t="n">
-        <v>7100539</v>
+        <v>7100491</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3214,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3219,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3259,13 +3254,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445069</t>
+          <t>https://artportalen.se/Sighting/135445059</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135445072</v>
+        <v>135445069</v>
       </c>
       <c r="B24" t="n">
         <v>57982</v>
@@ -3294,21 +3289,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613316</v>
+        <v>613582</v>
       </c>
       <c r="R24" t="n">
-        <v>7100665</v>
+        <v>7100539</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3340,7 +3330,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,14 +3340,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3380,13 +3375,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445072</t>
+          <t>https://artportalen.se/Sighting/135445069</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135445073</v>
+        <v>135445072</v>
       </c>
       <c r="B25" t="n">
         <v>57982</v>
@@ -3426,10 +3421,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613305</v>
+        <v>613316</v>
       </c>
       <c r="R25" t="n">
-        <v>7100667</v>
+        <v>7100665</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3461,7 +3456,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3471,7 +3466,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3501,13 +3496,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445073</t>
+          <t>https://artportalen.se/Sighting/135445072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445074</v>
+        <v>135445073</v>
       </c>
       <c r="B26" t="n">
         <v>57982</v>
@@ -3538,7 +3533,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3547,13 +3542,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613337</v>
+        <v>613305</v>
       </c>
       <c r="R26" t="n">
-        <v>7100678</v>
+        <v>7100667</v>
       </c>
       <c r="S26" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3582,7 +3577,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3592,7 +3587,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3622,13 +3617,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445074</t>
+          <t>https://artportalen.se/Sighting/135445073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135445076</v>
+        <v>135445074</v>
       </c>
       <c r="B27" t="n">
         <v>57982</v>
@@ -3657,19 +3652,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613591</v>
+        <v>613337</v>
       </c>
       <c r="R27" t="n">
-        <v>7100642</v>
+        <v>7100678</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3708,19 +3708,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3743,13 +3738,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445076</t>
+          <t>https://artportalen.se/Sighting/135445074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135445079</v>
+        <v>135445076</v>
       </c>
       <c r="B28" t="n">
         <v>57982</v>
@@ -3778,24 +3773,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613654</v>
+        <v>613591</v>
       </c>
       <c r="R28" t="n">
-        <v>7100656</v>
+        <v>7100642</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,7 +3814,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3834,14 +3824,19 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3864,16 +3859,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445079</t>
+          <t>https://artportalen.se/Sighting/135445076</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135445070</v>
+        <v>135445079</v>
       </c>
       <c r="B29" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,27 +3876,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3910,13 +3905,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613505</v>
+        <v>613654</v>
       </c>
       <c r="R29" t="n">
-        <v>7100621</v>
+        <v>7100656</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,7 +3950,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,54 +3980,59 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445070</t>
+          <t>https://artportalen.se/Sighting/135445079</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135445052</v>
+        <v>135445070</v>
       </c>
       <c r="B30" t="n">
-        <v>99315</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613795</v>
+        <v>613505</v>
       </c>
       <c r="R30" t="n">
-        <v>7100557</v>
+        <v>7100621</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445052</t>
+          <t>https://artportalen.se/Sighting/135445070</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135445058</v>
+        <v>135445052</v>
       </c>
       <c r="B31" t="n">
         <v>99315</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613724</v>
+        <v>613795</v>
       </c>
       <c r="R31" t="n">
-        <v>7100494</v>
+        <v>7100557</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,13 +4217,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445058</t>
+          <t>https://artportalen.se/Sighting/135445052</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135445067</v>
+        <v>135445058</v>
       </c>
       <c r="B32" t="n">
         <v>99315</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613619</v>
+        <v>613724</v>
       </c>
       <c r="R32" t="n">
-        <v>7100553</v>
+        <v>7100494</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,6 +4332,122 @@
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445058</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135445067</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ystaåmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>613619</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7100553</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445067</t>
         </is>
@@ -4370,6 +4486,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136916429</v>
+        <v>136916431</v>
       </c>
       <c r="B11" t="n">
         <v>101545</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613803</v>
+        <v>613699</v>
       </c>
       <c r="R11" t="n">
-        <v>7100627</v>
+        <v>7100529</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AC-Åse-0045</t>
+          <t>AC-Åse-0044</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1838,16 +1838,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916429</t>
+          <t>https://artportalen.se/Sighting/136916431</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136916431</v>
+        <v>135445043</v>
       </c>
       <c r="B12" t="n">
-        <v>101545</v>
+        <v>92027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,38 +1855,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ystaåmyran, Ås lm</t>
+          <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613699</v>
+        <v>613775</v>
       </c>
       <c r="R12" t="n">
-        <v>7100529</v>
+        <v>7100634</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1911,35 +1907,39 @@
           <t>Åsele</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>AC-Åse-0044</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1949,18 +1949,18 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136916431</t>
+          <t>https://artportalen.se/Sighting/135445043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445043</v>
+        <v>135445045</v>
       </c>
       <c r="B13" t="n">
         <v>92027</v>
@@ -1989,16 +1989,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613775</v>
+        <v>613799</v>
       </c>
       <c r="R13" t="n">
-        <v>7100634</v>
+        <v>7100628</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2030,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,6 +2052,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2070,54 +2074,51 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445043</t>
+          <t>https://artportalen.se/Sighting/135445045</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445045</v>
+        <v>135445042</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613799</v>
+        <v>613767</v>
       </c>
       <c r="R14" t="n">
-        <v>7100628</v>
+        <v>7100672</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2149,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,7 +2169,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445045</t>
+          <t>https://artportalen.se/Sighting/135445042</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445042</v>
+        <v>135445044</v>
       </c>
       <c r="B15" t="n">
         <v>79443</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613767</v>
+        <v>613799</v>
       </c>
       <c r="R15" t="n">
-        <v>7100672</v>
+        <v>7100626</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,13 +2306,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445042</t>
+          <t>https://artportalen.se/Sighting/135445044</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135445044</v>
+        <v>135445055</v>
       </c>
       <c r="B16" t="n">
         <v>79443</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613799</v>
+        <v>613807</v>
       </c>
       <c r="R16" t="n">
-        <v>7100626</v>
+        <v>7100543</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,13 +2422,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445044</t>
+          <t>https://artportalen.se/Sighting/135445055</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135445055</v>
+        <v>135445060</v>
       </c>
       <c r="B17" t="n">
         <v>79443</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613807</v>
+        <v>613717</v>
       </c>
       <c r="R17" t="n">
-        <v>7100543</v>
+        <v>7100503</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,13 +2538,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445055</t>
+          <t>https://artportalen.se/Sighting/135445060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135445060</v>
+        <v>135445065</v>
       </c>
       <c r="B18" t="n">
         <v>79443</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613717</v>
+        <v>613671</v>
       </c>
       <c r="R18" t="n">
-        <v>7100503</v>
+        <v>7100521</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445060</t>
+          <t>https://artportalen.se/Sighting/135445065</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135445065</v>
+        <v>135445068</v>
       </c>
       <c r="B19" t="n">
         <v>79443</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613671</v>
+        <v>613584</v>
       </c>
       <c r="R19" t="n">
-        <v>7100521</v>
+        <v>7100548</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,51 +2770,56 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445065</t>
+          <t>https://artportalen.se/Sighting/135445068</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135445068</v>
+        <v>135445049</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613584</v>
+        <v>613792</v>
       </c>
       <c r="R20" t="n">
-        <v>7100548</v>
+        <v>7100584</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2846,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,14 +2861,19 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2886,13 +2896,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445068</t>
+          <t>https://artportalen.se/Sighting/135445049</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135445049</v>
+        <v>135445057</v>
       </c>
       <c r="B21" t="n">
         <v>57982</v>
@@ -2923,7 +2933,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2932,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613792</v>
+        <v>613781</v>
       </c>
       <c r="R21" t="n">
-        <v>7100584</v>
+        <v>7100499</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2967,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,19 +2987,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3012,13 +3017,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445049</t>
+          <t>https://artportalen.se/Sighting/135445057</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135445057</v>
+        <v>135445059</v>
       </c>
       <c r="B22" t="n">
         <v>57982</v>
@@ -3047,21 +3052,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613781</v>
+        <v>613721</v>
       </c>
       <c r="R22" t="n">
-        <v>7100499</v>
+        <v>7100491</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,14 +3103,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3133,13 +3138,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445057</t>
+          <t>https://artportalen.se/Sighting/135445059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135445059</v>
+        <v>135445069</v>
       </c>
       <c r="B23" t="n">
         <v>57982</v>
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613721</v>
+        <v>613582</v>
       </c>
       <c r="R23" t="n">
-        <v>7100491</v>
+        <v>7100539</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3209,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3219,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3254,13 +3259,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445059</t>
+          <t>https://artportalen.se/Sighting/135445069</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135445069</v>
+        <v>135445072</v>
       </c>
       <c r="B24" t="n">
         <v>57982</v>
@@ -3289,16 +3294,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613582</v>
+        <v>613316</v>
       </c>
       <c r="R24" t="n">
-        <v>7100539</v>
+        <v>7100665</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3330,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3340,19 +3350,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3375,13 +3380,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445069</t>
+          <t>https://artportalen.se/Sighting/135445072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135445072</v>
+        <v>135445073</v>
       </c>
       <c r="B25" t="n">
         <v>57982</v>
@@ -3421,10 +3426,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613316</v>
+        <v>613305</v>
       </c>
       <c r="R25" t="n">
-        <v>7100665</v>
+        <v>7100667</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,7 +3461,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3466,7 +3471,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3496,13 +3501,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445072</t>
+          <t>https://artportalen.se/Sighting/135445073</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135445073</v>
+        <v>135445074</v>
       </c>
       <c r="B26" t="n">
         <v>57982</v>
@@ -3533,7 +3538,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3542,13 +3547,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613305</v>
+        <v>613337</v>
       </c>
       <c r="R26" t="n">
-        <v>7100667</v>
+        <v>7100678</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3577,7 +3582,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3587,7 +3592,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3617,13 +3622,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445073</t>
+          <t>https://artportalen.se/Sighting/135445074</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135445074</v>
+        <v>135445076</v>
       </c>
       <c r="B27" t="n">
         <v>57982</v>
@@ -3652,24 +3657,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613337</v>
+        <v>613591</v>
       </c>
       <c r="R27" t="n">
-        <v>7100678</v>
+        <v>7100642</v>
       </c>
       <c r="S27" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3708,14 +3708,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>skalad gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3738,13 +3743,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445074</t>
+          <t>https://artportalen.se/Sighting/135445076</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135445076</v>
+        <v>135445079</v>
       </c>
       <c r="B28" t="n">
         <v>57982</v>
@@ -3773,19 +3778,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613591</v>
+        <v>613654</v>
       </c>
       <c r="R28" t="n">
-        <v>7100642</v>
+        <v>7100656</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3814,7 +3824,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3824,19 +3834,14 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>skalad gran</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3859,16 +3864,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445076</t>
+          <t>https://artportalen.se/Sighting/135445079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135445079</v>
+        <v>135445070</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,27 +3881,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3905,13 +3910,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613654</v>
+        <v>613505</v>
       </c>
       <c r="R29" t="n">
-        <v>7100656</v>
+        <v>7100621</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3940,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,7 +3955,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,59 +3985,54 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445079</t>
+          <t>https://artportalen.se/Sighting/135445070</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135445070</v>
+        <v>135445052</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>99315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ystaåmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613505</v>
+        <v>613795</v>
       </c>
       <c r="R30" t="n">
-        <v>7100621</v>
+        <v>7100557</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445070</t>
+          <t>https://artportalen.se/Sighting/135445052</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135445052</v>
+        <v>135445058</v>
       </c>
       <c r="B31" t="n">
         <v>99315</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613795</v>
+        <v>613724</v>
       </c>
       <c r="R31" t="n">
-        <v>7100557</v>
+        <v>7100494</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,13 +4217,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445052</t>
+          <t>https://artportalen.se/Sighting/135445058</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135445058</v>
+        <v>135445067</v>
       </c>
       <c r="B32" t="n">
         <v>99315</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613724</v>
+        <v>613619</v>
       </c>
       <c r="R32" t="n">
-        <v>7100494</v>
+        <v>7100553</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4332,122 +4332,6 @@
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135445058</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>135445067</v>
-      </c>
-      <c r="B33" t="n">
-        <v>99315</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Ystaåmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>613619</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7100553</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445067</t>
         </is>
@@ -4486,7 +4370,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136916431</v>
       </c>
       <c r="B11" t="n">
-        <v>101545</v>
+        <v>101551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136916431</v>
       </c>
       <c r="B11" t="n">
-        <v>101551</v>
+        <v>101555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30058-2024 artfynd.xlsx
+++ b/artfynd/A 30058-2024 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136916431</v>
       </c>
       <c r="B11" t="n">
-        <v>101555</v>
+        <v>101557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
